--- a/P6.xlsx
+++ b/P6.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P6" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="표준 규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P6" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="표준 규칙" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'P6'!$A$1:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +37,16 @@
     <font>
       <b val="1"/>
       <color rgb="001F7A1F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,8 +66,12 @@
       <i val="1"/>
       <color rgb="00B00000"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +81,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E6E86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7EEF2"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -103,25 +128,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,27 +524,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="54" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Feature ID</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -534,45 +563,13 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>■ 정의</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>■ 원인 추정</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>■ 이후 나타날 가능성</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>■ Strong Co-occurrence</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>■ 추가 검증 포인트</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>■ 사고확장</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>pelvis_open_early</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -596,69 +593,13 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>다운스윙 중반(P6)에서 골반이 정상보다 이른 타이밍에 목표 방향으로 열리는 현상. 회전량(Amount)이 아니라 회전 시점(Timing)의 문제가 핵심이다.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>① Lead Pressure Early (조기 리드 압력)
-   → M-PRS-02 · 압력이 리드측으로 너무 빨리 이동한다.
-② Trail Leg Push Early (트레일 다리 조기 추진)
-   → M-ROT-12 · 트레일 다리의 추진이 골반을 조기에 연다.
-③ Thorax Open Early (흉곽 조기 오픈)
-   → M-ROT-02 · 팔 전달 전에 흉곽이 먼저 열린다.
-④ Body Rotation Dominant (몸통 회전 주도)
-   → M-ROT-13 · 몸통 회전이 다운스윙을 주도한다.</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>① → M-ARM-03 · 팔이 내려올 공간이 감소한다.
-   → Arm Drop Insufficient (팔 하강 부족)
-   → M-CLB-03 · 클럽이 가파른 전달 패턴으로 접근한다.
-   → Steep Shaft (가파른 샤프트)
-② → M-ARM-02 · 흉곽 회전이 팔 전달보다 앞선다.
-   → M-CLB-07 · 클럽페이스가 제시간에 스퀘어되지 못한다.
-   → Club Face Open (클럽페이스 오픈)
-③ → M-SPC-02 · 다운스윙 공간이 부족해진다.
-   → Handle Raise (핸들 상승)
-   → Early Extension (얼리 익스텐션)
-④ → M-ROT-02 · 팔 전달 전에 흉곽이 먼저 열린다.
-   → Thorax Open Early (흉곽 조기 오픈)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>· Thorax Open Early (흉곽 조기 오픈) — 상·하체 동시 조기 오픈, 공통원인 다수
-· Spin-out (스핀아웃) — 트레일측 회전축 공유
-· Pelvis Rotation Excessive (골반 과회전) — 회전량 동반형에서 함께 관찰</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>· Pelvis Open Early(타이밍)와 Pelvis Rotation Excessive(회전량)는 자주 함께 나타나지만, 회전량은 많아도 타이밍은 정상인 골퍼가 존재 → 두 축 분리 유지.
-· Pelvis Open Early와 Spin-out이 같은 현상의 다른 관점 표현인지 검증 필요.
-· 하체만 먼저 열리고 흉곽은 유지되는 Subtype 존재 여부 확인.
-· [재분류] 원본은 Arm Drop Insufficient를 '원인'으로 기재했으나, 본 표준에서는 인과 방향상 Possible Results(결과)로 이동함 — 임상 방향성 재확인.</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>· 골반은 3개의 독립 축으로 관리: Amount(Insufficient/Excessive) · Timing(Open Early) · Velocity(Stall). 이름이 비슷해도 평가 축이 다르다.
-· Pelvis Open Early는 Pressure 계열(Lead Pressure Early / Trail Leg Drive)에서 촉발되어 Arm·Club 계열 결과로 분기하는 Timing-Trigger Node 성격을 가진다.</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
           <t>refactored</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>pelvis_rotation_insufficient</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -680,23 +621,15 @@
           <t>Rotation/Amount · Insufficient</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>pelvis_rotation_excessive</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -718,23 +651,15 @@
           <t>Rotation/Amount · Excessive</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>pelvis_stall</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -756,23 +681,15 @@
           <t>Rotation/Velocity · Stall</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>thorax_rotation_insufficient</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -794,23 +711,15 @@
           <t>Rotation/Amount · Insufficient</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>thorax_rotation_excessive</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -832,23 +741,15 @@
           <t>Rotation/Amount · Excessive</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>thorax_stall</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -870,23 +771,15 @@
           <t>Rotation/Velocity · Stall</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>thorax_open_early</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -908,23 +801,15 @@
           <t>Rotation/Timing · Early</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>early_extension</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -948,69 +833,13 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>다운스윙 중반(P6)에서 골반이 볼 방향으로 전진하거나 고관절 굴곡이 조기에 소실되며 몸이 일찍 일어나는 현상. 골반·고관절·척추 자세를 유지하지 못하고 신체가 조기에 신전되는 것이 핵심이다.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>① Lead Pressure Insufficient (리드측 압력 부족)
-   → M-PRS-03 · 임팩트 전까지 압력이 리드측에 도달하지 못한다.
-② Pelvis Stall (골반 회전 정지)
-   → M-ROT-05 · 임팩트 전에 골반 회전이 감속한다.
-   → M-ROT-10 · 리드측이 주 회전축이 되지 못한다.
-③ Arm Stuck (팔 끼임)
-   → M-SPC-02 · 다운스윙 공간이 부족해진다.
-   → M-CMP-04 · 공간을 만들기 위해 몸이 일찍 신전한다.
-④ Steep Shaft (가파른 샤프트)
-   → M-CMP-04 · 공간을 만들기 위해 몸이 일찍 신전한다.</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>① → M-SPC-02 · 다운스윙 공간이 부족해진다.
-   → Handle Raise (핸들 상승)
-② → M-ARM-01 · 회전하는 몸에 비해 팔이 뒤처진다.
-   → Arm Stuck (팔 끼임)
-   → Late Release (늦은 릴리즈)
-③ → M-CMP-04 · 공간을 만들기 위해 몸이 일찍 신전한다.
-   → Spine Extension Excessive (척추 과신전)
-   → Head Elevation (머리 상승)
-④ → M-CLB-06 · 클럽헤드가 손보다 먼저 앞선다.
-   → Flip Release (플립 릴리즈)</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>· Pelvis Stall (골반 회전 정지) — 선후 개인차, 매우 높은 동반
-· Spine Extension Excessive (척추 과신전) — 분절만 다른 동반 신전
-· Head Elevation (머리 상승)
-· Hanging Back (체중 뒤잔류)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>· Early Extension은 원인이 여러 갈래(Pelvis/Space/Balance/Shaft)이므로 '왜 일어났는가'를 함께 기록해야 Graph 품질이 오른다.
-· Pelvis Stall과 Early Extension의 선행 관계는 개인차 → Strong Co-occurrence로 관리.
-· [재분류] 원본에서 Head Elevation을 원인/동반으로 혼용 — 본 표준에서는 인과 결과(Possible Results) + 강동반(Strong Co-occurrence) 성격을 구분해 각각 기재.</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>· Early Extension은 In-degree·Out-degree가 모두 높은 Hub Node다. Subtype(Pelvis / Space / Balance / Shaft Type)을 태그로 관리.
-· 공통 보상 언어 M-CMP-04(공간을 만들기 위해 몸이 일찍 신전한다)는 Spine Extension Excessive·Head Elevation 등 다수 Feature에서 재사용된다.</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
           <t>refactored</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>spine_extension_excessive</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -1032,23 +861,15 @@
           <t>Magnitude · Excessive</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>head_elevation</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -1070,23 +891,15 @@
           <t>Position/Height · Rise</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>head_drop</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -1108,23 +921,15 @@
           <t>Position/Height · Drop</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>head_hanging_back</t>
-        </is>
+      <c r="A14" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -1146,23 +951,15 @@
           <t>Position/Location · Trail</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>high_hands</t>
-        </is>
+      <c r="A15" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -1186,66 +983,13 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>다운스윙 중반(P6)에서 몸의 회전·다운스윙 진행 정도에 비해 손이 정상보다 높은 위치에 있는 현상. 절대 높이가 아니라 몸의 회전 대비 손이 충분히 하강하지 못한 상대 위치가 핵심이다.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>※ P6의 원인은 대개 P4에서 시작된다 (P4 Initial Condition → Transition Mechanism → P6 Observation).
-① Arm Depth Excessive (P4, 백스윙 손 과도한 깊이)
-   → M-ARM-07 · 손이 몸통보다 뒤쪽에서 다운스윙을 시작한다.
-   → M-ROT-03 · 전환 구간에서 흉곽이 급격하게 회전한다.
-   → M-ARM-08 · 급격한 흉곽 회전으로 팔이 하강할 시간이 부족해진다.
-② Arm Drop Insufficient (팔 하강 부족)
-   → M-ARM-10 · 다운스윙 동안 팔의 수직 하강이 충분하지 않다.
-③ Early Extension (얼리 익스텐션)
-   → M-SPC-02 · 다운스윙 공간이 부족해진다.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>① → M-CLB-03 · 클럽이 가파른 전달 패턴으로 접근한다.
-   → Steep Shaft (가파른 샤프트)
-② → M-CLB-07 · 클럽페이스가 제시간에 스퀘어되지 못한다.
-   → Club Face Open (클럽페이스 오픈)
-③ → M-ARM-01 · 회전하는 몸에 비해 팔이 뒤처진다.
-   → Arm Stuck (팔 끼임)
-   → Late Release (늦은 릴리즈)
-④ → M-CLB-02 · 클럽이 바깥쪽 경로로 접근한다.
-   → Outside Delivery (아웃사이드 딜리버리)</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>· Steep Shaft (가파른 샤프트)
-· Handle Raise (핸들 상승)
-· Early Extension (얼리 익스텐션)
-· Head Elevation (머리 상승)</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>· High Hands가 '손이 높아서'인지 '몸의 회전에 비해 손이 늦게 내려와서'인지 레슨 데이터로 구분 필요 (후자 가능성 높음).
-· High Hands → Steep Shaft는 흔한 조합이나, 높은 손에서도 샤프트를 눕혀 전달하는 예외 골퍼 존재 여부 확인.</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>· P6 손 위치 Feature는 모두 상대 위치(Relative Position): '이 시점의 다운스윙 진행에서 정상이라면 손이 어디 있어야 하는가' 기준. High/Low/Deep/Shallow 전부 동일 철학.
-· High Hands는 P4→Transition→P6를 잇는 Cross-Phase Chain의 대표 사례. P7 Steep Shaft/Outside Delivery로 이어진다.</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
           <t>refactored</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>low_hands</t>
-        </is>
+      <c r="A16" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -1267,23 +1011,15 @@
           <t>Position/Height · Low (Relative)</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>deep_hands</t>
-        </is>
+      <c r="A17" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -1305,23 +1041,15 @@
           <t>Position/Depth · Deep</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>forward_hands</t>
-        </is>
+      <c r="A18" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -1343,23 +1071,15 @@
           <t>Position/Direction · Forward</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>hands_too_far_from_body</t>
-        </is>
+      <c r="A19" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -1381,23 +1101,15 @@
           <t>Relationship · Far</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>hands_too_close_to_body</t>
-        </is>
+      <c r="A20" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -1419,23 +1131,15 @@
           <t>Relationship · Close</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>late_arm</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -1457,23 +1161,15 @@
           <t>Timing · Late</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>trail_elbow_behind_body</t>
-        </is>
+      <c r="A22" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -1495,23 +1191,15 @@
           <t>Location · Trail</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>steep_shaft</t>
-        </is>
+      <c r="A23" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
@@ -1533,23 +1221,15 @@
           <t>Angle/Plane · Steep</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>shallow_shaft</t>
-        </is>
+      <c r="A24" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
@@ -1571,23 +1251,15 @@
           <t>Angle/Plane · Shallow</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>casting</t>
-        </is>
+      <c r="A25" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
@@ -1609,23 +1281,15 @@
           <t>Release · Cast</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>lead_pressure_insufficient</t>
-        </is>
+      <c r="A26" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
@@ -1647,23 +1311,15 @@
           <t>Location/Magnitude · Lead·Insufficient</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>lead_pressure_excessive</t>
-        </is>
+      <c r="A27" s="2" t="n">
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
@@ -1685,23 +1341,15 @@
           <t>Location/Magnitude · Lead·Excessive</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>incomplete_pressure_transfer</t>
-        </is>
+      <c r="A28" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -1723,23 +1371,15 @@
           <t>Timing · Late</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>spin_out</t>
-        </is>
+      <c r="A29" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
@@ -1761,20 +1401,14 @@
           <t>Pattern · Spin-out</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1785,116 +1419,1296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Pelvis Open Early  (골반 조기 오픈)   ·   Pelvis / Rotation/Timing · Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>■ 정의</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>다운스윙 중반(P6)에서 골반이 정상보다 이른 타이밍에 목표 방향으로 열리는 현상. 회전량(Amount)이 아니라 회전 시점(Timing)의 문제가 핵심이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>■ 원인 추정</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Lead Pressure Early (조기 리드 압력)
+   ↓
+Pressure Transfers To The Lead Side Too Early.
+(압력이 리드측으로 너무 빨리 이동한다.)
+   ↓
+Pelvis Open Early (골반 조기 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Trail Leg Push Early (트레일 다리 조기 추진)
+   ↓
+Trail Leg Drive Opens The Pelvis Early.
+(트레일 다리의 추진이 골반을 조기에 연다.)
+   ↓
+Pelvis Open Early (골반 조기 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Thorax Open Early (흉곽 조기 오픈)
+   ↓
+The Thorax Opens Before Arm Delivery.
+(팔 전달 전에 흉곽이 먼저 열린다.)
+   ↓
+Pelvis Open Early (골반 조기 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Body Rotation Dominant (몸통 회전 주도)
+   ↓
+Body Rotation Leads The Downswing.
+(몸통 회전이 다운스윙을 주도한다.)
+   ↓
+Pelvis Open Early (골반 조기 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>■ 이후 나타날 가능성</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Pelvis Open Early (골반 조기 오픈)
+   ↓
+Arm Delivery Space Is Reduced.
+(팔이 내려올 공간이 감소한다.)
+   ↓
+Arm Drop Insufficient (팔 하강 부족)
+   ↓
+The Club Approaches From A Steeper Delivery Pattern.
+(클럽이 가파른 전달 패턴으로 접근한다.)
+   ↓
+Steep Shaft (가파른 샤프트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Pelvis Open Early (골반 조기 오픈)
+   ↓
+Thorax Rotation Outpaces Arm Delivery.
+(흉곽 회전이 팔 전달보다 앞선다.)
+   ↓
+The Club Face Cannot Square In Time.
+(클럽페이스가 제시간에 스퀘어되지 못한다.)
+   ↓
+Club Face Open (클럽페이스 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Pelvis Open Early (골반 조기 오픈)
+   ↓
+The Body Loses Delivery Space.
+(다운스윙 공간이 부족해진다.)
+   ↓
+Handle Raise (핸들 상승)
+   ↓
+Early Extension (얼리 익스텐션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Pelvis Open Early (골반 조기 오픈)
+   ↓
+The Thorax Opens Before Arm Delivery.
+(팔 전달 전에 흉곽이 먼저 열린다.)
+   ↓
+Thorax Open Early (흉곽 조기 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>■ Strong Co-occurrence</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>· Thorax Open Early (흉곽 조기 오픈) — 상·하체 동시 조기 오픈, 공통원인 다수
+· Spin-out (스핀아웃) — 트레일측 회전축 공유
+· Pelvis Rotation Excessive (골반 과회전) — 회전량 동반형에서 함께 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>■ 추가 검증 포인트</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>· Pelvis Open Early(타이밍)와 Pelvis Rotation Excessive(회전량)는 자주 함께 나타나지만, 회전량은 많아도 타이밍은 정상인 골퍼가 존재 → 두 축 분리 유지.
+· Pelvis Open Early와 Spin-out이 같은 현상의 다른 관점 표현인지 검증 필요.
+· 하체만 먼저 열리고 흉곽은 유지되는 Subtype 존재 여부 확인.
+· [재분류] 원본은 Arm Drop Insufficient를 '원인'으로 기재했으나 인과 방향상 결과로 이동함 — 임상 방향 재확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>■ 사고확장</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>· 골반은 3개 독립 축으로 관리: Amount(Insufficient/Excessive) · Timing(Open Early) · Velocity(Stall). 이름이 비슷해도 평가 축이 다르다.
+· Pelvis Open Early는 Pressure 계열에서 촉발되어 Arm·Club 계열 결과로 분기하는 Timing-Trigger Node 성격을 가진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Pelvis Rotation Insufficient  (골반 회전 부족)   ·   Pelvis / Rotation/Amount · Insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Pelvis Rotation Excessive  (골반 과회전)   ·   Pelvis / Rotation/Amount · Excessive</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Pelvis Stall  (골반 회전 정지)   ·   Pelvis / Rotation/Velocity · Stall</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Thorax Rotation Insufficient  (흉곽 회전 부족)   ·   Thorax / Rotation/Amount · Insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Thorax Rotation Excessive  (흉곽 과회전)   ·   Thorax / Rotation/Amount · Excessive</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Thorax Stall  (흉곽 회전 정지)   ·   Thorax / Rotation/Velocity · Stall</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Thorax Open Early  (흉곽 조기 오픈)   ·   Thorax / Rotation/Timing · Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Early Extension  (얼리 익스텐션)   ·   Pelvis / Pattern · Early Extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>■ 정의</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>다운스윙 중반(P6)에서 골반이 볼 방향으로 전진하거나 고관절 굴곡이 조기에 소실되며 몸이 일찍 일어나는 현상. 골반·고관절·척추 자세를 유지하지 못하고 신체가 조기에 신전되는 것이 핵심이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>■ 원인 추정</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Lead Pressure Insufficient (리드측 압력 부족)
+   ↓
+Pressure Does Not Reach The Lead Side Before Impact.
+(임팩트 전까지 압력이 리드측에 도달하지 못한다.)
+   ↓
+Early Extension (얼리 익스텐션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Pelvis Stall (골반 회전 정지)
+   ↓
+Pelvis Rotation Decelerates Before Impact.
+(임팩트 전에 골반 회전이 감속한다.)
+   ↓
+The Lead Side Cannot Become The Primary Rotation Axis.
+(리드측이 주 회전축이 되지 못한다.)
+   ↓
+Early Extension (얼리 익스텐션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Arm Stuck (팔 끼임)
+   ↓
+The Body Loses Delivery Space.
+(다운스윙 공간이 부족해진다.)
+   ↓
+The Body Extends Early To Create Space.
+(공간을 만들기 위해 몸이 일찍 신전한다.)
+   ↓
+Early Extension (얼리 익스텐션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Steep Shaft (가파른 샤프트)
+   ↓
+The Body Extends Early To Create Space.
+(공간을 만들기 위해 몸이 일찍 신전한다.)
+   ↓
+Early Extension (얼리 익스텐션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>■ 이후 나타날 가능성</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Early Extension (얼리 익스텐션)
+   ↓
+The Body Loses Delivery Space.
+(다운스윙 공간이 부족해진다.)
+   ↓
+Handle Raise (핸들 상승)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Early Extension (얼리 익스텐션)
+   ↓
+The Arms Fall Behind The Rotating Body.
+(회전하는 몸에 비해 팔이 뒤처진다.)
+   ↓
+Arm Stuck (팔 끼임)
+   ↓
+Late Release (늦은 릴리즈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Early Extension (얼리 익스텐션)
+   ↓
+The Body Extends Early To Create Space.
+(공간을 만들기 위해 몸이 일찍 신전한다.)
+   ↓
+Spine Extension Excessive (척추 과신전)
+   ↓
+Head Elevation (머리 상승)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Early Extension (얼리 익스텐션)
+   ↓
+The Clubhead Overtakes The Hands Early.
+(클럽헤드가 손보다 먼저 앞선다.)
+   ↓
+Flip Release (플립 릴리즈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>■ Strong Co-occurrence</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>· Pelvis Stall (골반 회전 정지) — 선후 개인차, 매우 높은 동반
+· Spine Extension Excessive (척추 과신전) — 분절만 다른 동반 신전
+· Head Elevation (머리 상승)
+· Hanging Back (체중 뒤잔류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>■ 추가 검증 포인트</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>· Early Extension은 원인이 여러 갈래(Pelvis/Space/Balance/Shaft)이므로 '왜 일어났는가'를 함께 기록해야 Graph 품질이 오른다.
+· Pelvis Stall과 Early Extension의 선행 관계는 개인차 → Strong Co-occurrence로 관리.
+· [재분류] 원본에서 Head Elevation을 원인/동반으로 혼용 — 본 표준에서는 결과(Possible Results) + 강동반(Strong Co-occurrence)로 구분 기재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>■ 사고확장</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>· Early Extension은 In-degree·Out-degree가 모두 높은 Hub Node. Subtype(Pelvis / Space / Balance / Shaft Type)을 태그로 관리.
+· 공통 보상 언어 'The Body Extends Early To Create Space.'는 Spine Extension Excessive·Head Elevation 등 다수 Feature에서 재사용된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Spine Extension Excessive  (척추 과신전)   ·   Spine / Magnitude · Excessive</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Head Elevation  (머리 상승)   ·   Head / Position/Height · Rise</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Head Drop  (머리 하강)   ·   Head / Position/Height · Drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Head Hanging Back  (머리 뒤잔류)   ·   Head / Position/Location · Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>High Hands  (손 높음)   ·   Hands / Position/Height · High (Relative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>■ 정의</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>다운스윙 중반(P6)에서 몸의 회전·다운스윙 진행 정도에 비해 손이 정상보다 높은 위치에 있는 현상. 절대 높이가 아니라 몸의 회전 대비 손이 충분히 하강하지 못한 상대 위치가 핵심이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>■ 원인 추정</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Arm Depth Excessive (P4, 백스윙 손 과도한 깊이)
+   ↓
+The Hands Start Downswing From Behind The Thorax.
+(손이 몸통보다 뒤쪽에서 다운스윙을 시작한다.)
+   ↓
+The Thorax Rotates Rapidly During Transition.
+(전환 구간에서 흉곽이 급격하게 회전한다.)
+   ↓
+Rapid Thorax Rotation Reduces Available Arm Drop Time.
+(급격한 흉곽 회전으로 팔이 하강할 시간이 부족해진다.)
+   ↓
+High Hands (손 높음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Arm Drop Insufficient (팔 하강 부족)
+   ↓
+Vertical Arm Drop During Downswing Is Insufficient.
+(다운스윙 동안 팔의 수직 하강이 충분하지 않다.)
+   ↓
+High Hands (손 높음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Early Extension (얼리 익스텐션)
+   ↓
+The Body Loses Delivery Space.
+(다운스윙 공간이 부족해진다.)
+   ↓
+High Hands (손 높음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>■ 이후 나타날 가능성</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>High Hands (손 높음)
+   ↓
+The Club Approaches From A Steeper Delivery Pattern.
+(클럽이 가파른 전달 패턴으로 접근한다.)
+   ↓
+Steep Shaft (가파른 샤프트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>High Hands (손 높음)
+   ↓
+The Club Face Cannot Square In Time.
+(클럽페이스가 제시간에 스퀘어되지 못한다.)
+   ↓
+Club Face Open (클럽페이스 오픈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr"/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>High Hands (손 높음)
+   ↓
+The Arms Fall Behind The Rotating Body.
+(회전하는 몸에 비해 팔이 뒤처진다.)
+   ↓
+Arm Stuck (팔 끼임)
+   ↓
+Late Release (늦은 릴리즈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>High Hands (손 높음)
+   ↓
+The Club Approaches From Outside.
+(클럽이 바깥쪽 경로로 접근한다.)
+   ↓
+Outside Delivery (아웃사이드 딜리버리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>■ Strong Co-occurrence</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>· Steep Shaft (가파른 샤프트)
+· Handle Raise (핸들 상승)
+· Early Extension (얼리 익스텐션)
+· Head Elevation (머리 상승)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>■ 추가 검증 포인트</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>· High Hands가 '손이 높아서'인지 '몸의 회전에 비해 손이 늦게 내려와서'인지 레슨 데이터로 구분 필요 (후자 가능성 높음).
+· High Hands → Steep Shaft는 흔한 조합이나, 높은 손에서도 샤프트를 눕혀 전달하는 예외 골퍼 존재 여부 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>■ 사고확장</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>· P6 손 위치 Feature는 모두 상대 위치(Relative Position): '이 시점의 다운스윙 진행에서 정상이라면 손이 어디 있어야 하는가' 기준. High/Low/Deep/Shallow 전부 동일 철학.
+· High Hands는 P4→Transition→P6를 잇는 Cross-Phase Chain의 대표 사례. P7 Steep Shaft/Outside Delivery로 이어진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Low Hands  (손 낮음)   ·   Hands / Position/Height · Low (Relative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Deep Hands  (손 깊음)   ·   Hands / Position/Depth · Deep</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Forward Hands  (손 전방)   ·   Hands / Position/Direction · Forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Hands Too Far From Body  (손이 몸에서 멀어짐)   ·   Hands / Relationship · Far</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Hands Too Close To Body  (손이 몸에 가까움)   ·   Hands / Relationship · Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Late Arm  (팔 하강 지연)   ·   Arm / Timing · Late</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Trail Elbow Behind Body  (트레일 팔꿈치 뒤처짐)   ·   Trail Elbow / Location · Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Steep Shaft  (가파른 샤프트)   ·   Shaft / Angle/Plane · Steep</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Shallow Shaft  (눕는 샤프트)   ·   Shaft / Angle/Plane · Shallow</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Casting  (캐스팅)   ·   Club / Release · Cast</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Lead Pressure Insufficient  (리드측 압력 부족)   ·   Pressure / Location/Magnitude · Lead·Insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Lead Pressure Excessive  (리드측 압력 과다)   ·   Pressure / Location/Magnitude · Lead·Excessive</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Incomplete Pressure Transfer  (압력 이동 미완성)   ·   Pressure / Timing · Late</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Spin-out  (스핀아웃)   ·   Pelvis / Pattern · Spin-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>(상태)</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>표준화 예정 — 원본 P6 기준 순차 진행 (6섹션: 정의 / 원인 추정 / 이후 나타날 가능성 / Strong Co-occurrence / 추가 검증 포인트 / 사고확장)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>P6 Feature 표준 구조 (고정)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>모든 Feature는 아래 6개 섹션만 사용한다:</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>각 Feature는 세로 블록으로 작성하며, 아래 6개 섹션만 사용한다:</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  ■ 정의  /  ■ 원인 추정  /  ■ 이후 나타날 가능성  /  ■ Strong Co-occurrence  /  ■ 추가 검증 포인트  /  ■ 사고확장</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>항목 구분 기준 (혼용 금지)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>· 원인 추정        : 현재 Feature를 발생시키는 선행 원인 (인과, 상류)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>· 이후 나타날 가능성 : 현재 Feature 이후 생체역학적으로 발생 가능한 결과 (인과, 하류)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>· Strong Co-occurrence : 직접 인과가 아니어도 레슨상 약 75%+ 함께 관찰되는 Feature (공통원인 포함)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>· 'Observation' 항목은 사용하지 않는다 — Feature 자체가 이미 Observation이다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Mechanism 표기 규칙</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Mechanism 표기 규칙 (현재 단계)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>· 원인/결과 체인의 모든 연결 문장은 Mechanism_Dictionary.xlsx의 M-ID로 표기한다.  형식:  → M-XXX-NN · 표준 한글 문장</t>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>· 원인/결과 체인의 연결 문장은 Mechanism을 '영문 문장 ↓ (한글 문장)' 형태로 표기한다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>· 같은 의미의 링크는 항상 같은 M-ID를 재사용한다. 새 표현이 필요하면 Dictionary에 먼저 등록 후 사용한다.</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>· 예:   Feature A  ↓  The Thorax Opens Before Arm Delivery. (팔 전달 전에 흉곽이 먼저 열린다.)  ↓  Feature B</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>· 같은 의미의 링크는 항상 같은 표준 문장을 재사용한다. 새 표현은 Mechanism_Dictionary.xlsx에 먼저 등록 후 사용한다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>· Mechanism ID는 부여하지 않는다 — Dictionary 안정화 이후 일괄 부여 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>작업 상태</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>· refactored = 6섹션 표준화 완료 (현재: pelvis_open_early, early_extension, high_hands)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>· pending    = 표준화 예정 (원본 P6.xlsx 내용 기준으로 순차 리팩토링)</t>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>· refactored = 6섹션 표준화 완료 (현재: Pelvis Open Early, Early Extension, High Hands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>· pending    = 표준화 예정 (원본 P6 내용 기준으로 순차 리팩토링)</t>
         </is>
       </c>
     </row>
